--- a/rmonize/data_proc_elem/DPE_CARLA_P2.xlsx
+++ b/rmonize/data_proc_elem/DPE_CARLA_P2.xlsx
@@ -1618,10 +1618,10 @@
       <c r="H25" t="inlineStr">
         <is>
           <t>case_when(                                                                                                                                                                                                                                                                                                                                                                                                                                _x000D_
-  hyp_i == 1 ~ 1, _x000D_
-  hyp_i == 2 ~ 0, _x000D_
-  is.na(hyp_i) &amp; htn_kora == 1 ~ 1,_x000D_
-  is.na(hyp_i) &amp; htn_kora == 0 ~ 0, _x000D_
+  hyp_i == 1 | htn_kora == 1 ~ 1, _x000D_
+  hyp_i == 2 &amp; htn_kora == 0 ~ 0, _x000D_
+  is.na(hyp_i) &amp; htn_kora == 0 ~ 0,_x000D_
+  is.na(htn_kora) &amp; hyp_i == 2 ~ 0, _x000D_
   TRUE ~ NA_integer_)</t>
         </is>
       </c>
@@ -2903,10 +2903,12 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>case_when(_x000D_
-      f1_htn_kora == 1 | f2_htn_kora == 1 ~ 1,_x000D_
-      f1_htn_kora == 0 &amp; f2_htn_kora == 0 ~ 0,_x000D_
-      TRUE ~ NA_integer__x000D_
-    )</t>
+  f1_htn_kora == 1 | f2_htn_kora == 1 ~ 1,_x000D_
+  f1_htn_kora == 0 &amp; f2_htn_kora == 0 ~ 0,_x000D_
+  is.na(f1_htn_kora) &amp; f2_htn_kora == 0 ~ 0,_x000D_
+  is.na(f2_htn_kora) &amp; f1_htn_kora == 0 ~ 0,_x000D_
+  TRUE ~ NA_integer__x000D_
+)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3081,7 +3083,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>as.numeric(f2_insuff_date-gebdat)/365.25</t>
+          <t>as.numeric(as.Date(f2_insuff_date)-as.Date(gebdat))/365.25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5017,12 +5019,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>mna*1000</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
